--- a/output/laminas_comunales/comunal_s_fonasa_a_2023_los_rios.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2023_los_rios.xlsx
@@ -375,166 +375,166 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Valdivia</t>
+          <t>Corral</t>
         </is>
       </c>
       <c r="C2">
-        <v>147970</v>
+        <v>94.70820041283542</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Panguipulli</t>
+          <t>Mariquina</t>
         </is>
       </c>
       <c r="C3">
-        <v>39295</v>
+        <v>94.68474787623724</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>Lanco</t>
         </is>
       </c>
       <c r="C4">
-        <v>38399</v>
+        <v>94.35690913667254</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>14203</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mariquina</t>
+          <t>Lago Ranco</t>
         </is>
       </c>
       <c r="C5">
-        <v>24298</v>
+        <v>94.30874647319629</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Máfil</t>
         </is>
       </c>
       <c r="C6">
-        <v>21915</v>
+        <v>94.03878381613599</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14107</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Paillaco</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="C7">
-        <v>21651</v>
+        <v>93.66185144029404</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lanco</t>
+          <t>Paillaco</t>
         </is>
       </c>
       <c r="C8">
-        <v>18744</v>
+        <v>93.51675881133379</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Futrono</t>
+          <t>Panguipulli</t>
         </is>
       </c>
       <c r="C9">
-        <v>16888</v>
+        <v>93.09405354181473</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lago Ranco</t>
+          <t>Futrono</t>
         </is>
       </c>
       <c r="C10">
-        <v>11699</v>
+        <v>92.6537554177868</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Máfil</t>
+          <t>La Unión</t>
         </is>
       </c>
       <c r="C11">
-        <v>7856</v>
+        <v>89.66282165039929</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Corral</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="C12">
-        <v>5047</v>
+        <v>83.37277439711517</v>
       </c>
     </row>
   </sheetData>
@@ -590,7 +590,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/laminas_comunales/comunal_s_fonasa_a_2023_los_rios.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2023_los_rios.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C375"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -535,6 +535,5451 @@
       </c>
       <c r="C12">
         <v>83.37277439711517</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>49.18371176580972</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>48.17518248175183</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>47.91810642709054</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>47.87623723793936</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>47.40024183796856</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>47.3785013167345</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>47.2636815920398</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>47.24858726065727</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>47.07667321993333</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>46.90850463522773</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>46.80851063829788</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>46.66028249940148</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>46.58517822036072</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>46.27796198570962</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>46.18172665492072</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>45.83037194977494</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>45.59865238424326</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>45.52448864702571</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>45.40516815712953</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>44.03707459995493</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>43.38485966468968</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>40.60988251554942</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>39.85662915051604</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>39.39088849735716</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>39.38662423876666</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>39.33569979716025</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>39.28254735993551</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>38.44773057526285</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>38.05362700502753</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>37.64308500656784</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>37.51071623412049</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>36.18099976308932</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>36.03391931485238</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>28.39611466477138</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>27.90810157194679</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>26.49652842934885</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>24.66292572675551</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>23.26767981565809</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>23.11603322426378</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>22.3126645918123</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>21.57876741601846</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>21.5186592950933</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>20.88686049132297</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>20.3255925305243</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>20.09146080861612</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>19.71787078170057</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>19.04917573436697</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>18.96300025169897</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>18.8966034903359</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>18.85667523965396</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>18.04595715272979</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>17.99140708915145</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>17.73315819103021</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>17.61123607834531</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>16.93200663349917</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>16.87814220732583</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>16.86383085829348</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>16.75130995566304</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>16.69800837678434</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>16.63466286278598</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>16.38206042409458</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>16.20162404975812</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>15.64443676572218</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>15.62273276904474</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>15.48958582714867</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>15.39485359361136</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>15.27609834744055</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>15.23785552479235</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>14.98155326203708</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>14.92063492063492</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>14.67646807419437</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>14.29911803340214</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>14.14932585145351</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>14.0724946695096</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>14.04608970024792</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>13.79861273478295</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>13.70249181978354</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>13.7001352265044</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>13.68299775058978</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>13.59630419331912</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>13.54389264039662</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>13.49097492730565</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>13.39493011134802</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>13.39478094326071</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>13.3885508226279</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>13.37386018237082</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>13.37084031601628</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>13.36478850057607</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>13.34689968877185</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>13.3422598479613</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>13.08834633778002</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>13.08231472775451</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>13.0341446923597</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>12.99683733652449</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>12.98555075999249</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>12.95784381478922</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>12.93027005239823</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>12.92328956461645</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>12.89296099193504</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>12.8920277711276</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>12.88698716335263</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>12.81698033904637</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>12.80666897028335</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>12.79323513366067</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>12.79322853688029</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>12.76560967636483</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>12.75185936443543</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>12.70455461507457</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>12.63804372323642</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>12.58363563079403</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>12.49230040274816</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>12.41131720659885</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>12.40938166311301</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>12.32895904357166</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>12.31311351623458</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>12.08007581141909</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>12.02239507650227</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>11.99738476626348</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>11.91593169450178</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>11.84199919387344</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>11.77451064193521</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>11.76944374528065</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>11.72985131947111</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>11.71286425017768</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>11.67498765567565</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>11.67198348658285</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>11.64581924723912</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>11.63514484079483</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>11.6280882238329</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>11.57074669446426</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>11.55939200600488</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>11.51520387007602</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>11.47611253994233</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>11.46769177608846</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>11.40207310420076</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>11.38182733450793</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>11.18712931396815</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>10.95596133190118</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>10.92301491334139</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>10.78487716925851</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>10.727969348659</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>10.37826191046205</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>9.832989303809345</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>9.745323416723011</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>7.149862233222809</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>6.837953572233491</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>5.80009015100293</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>4.189044038668099</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>3.841559612350687</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>3.821369343757404</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>3.591094086665071</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>3.571624513084984</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>3.511575673807878</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>3.350768224910101</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>3.253838360221339</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>3.0429951277887</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>2.96081819455471</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>2.904606091115026</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>2.902055622732769</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>2.85231750797523</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>2.671850349335136</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>2.660018030200586</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>2.286329901843428</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>2.280580511402903</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>2.262497038616442</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>2.174329501915709</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>2.0738464914687</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>2.073104200763775</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>2.067275185936444</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>2.063894523326572</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>2.034595447374352</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>2.012992563466963</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>1.965855307640298</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>1.832368487289202</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>1.820228936010509</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>1.765417170495768</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>1.558872305140962</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>1.497778021616283</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>1.478074067155466</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>1.474532341672301</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>1.42438584629254</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>1.318458417849899</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>1.304764184821642</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>1.230995162404976</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>1.19320039228506</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>1.180734159457564</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>1.169850091066175</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>1.139494699481623</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>1.136638452237001</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>1.117308992562542</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>1.072237603825824</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>1.048428524727969</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>1.032088571964721</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>1.030002564321737</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>1.015031098825155</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>1.013323325201726</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>1.004005047457069</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>0.999392892168309</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>0.9476427386875148</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>0.9430286026030706</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>0.9413541404480241</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>0.9293419885116518</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>0.9217141489107015</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>0.850898410504492</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>0.8379219535551832</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>0.8339276896911175</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>0.8291306949311907</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>0.8126036484245439</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>0.8102345415778252</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>0.8061265618702136</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>0.7900406990663156</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>0.7699597251836058</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>0.7688320663441603</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>0.7658898799794517</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>0.743653303701171</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>0.7351055645781691</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>0.7285293980292346</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>0.713116670563479</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>0.712681409813407</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>0.7075141269322375</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>0.6997235659986178</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>0.6858389837113241</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>0.6755488834678176</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>0.6583672492219296</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>0.6507676720442678</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>0.6496281733481494</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>0.6449012494961709</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>0.6327931630318031</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>0.630932133647885</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>0.6301824212271974</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>0.6191794613642084</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>0.610485994733062</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>0.6091115026428392</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>0.6040775232821546</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>0.5993840322198531</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C248">
+        <v>0.5965336557839581</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C249">
+        <v>0.5962122983399579</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C250">
+        <v>0.5925275689910572</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C251">
+        <v>0.5870412026115104</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C252">
+        <v>0.5812462603641337</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C253">
+        <v>0.5760684698524168</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C254">
+        <v>0.5626047402441944</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C255">
+        <v>0.5596093707137763</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C256">
+        <v>0.5386357915932545</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C257">
+        <v>0.5355908776779544</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C258">
+        <v>0.5299664874132959</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C259">
+        <v>0.5254269093638582</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C260">
+        <v>0.5239822652156388</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C261">
+        <v>0.5235726131248519</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C262">
+        <v>0.5188343994314144</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C263">
+        <v>0.5093579720445393</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C264">
+        <v>0.5066616626008632</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C265">
+        <v>0.5027531721331099</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C266">
+        <v>0.5027531721331099</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C267">
+        <v>0.4937729741592143</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C268">
+        <v>0.4917372027408303</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C269">
+        <v>0.4914949995726131</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C270">
+        <v>0.4882866077796675</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C271">
+        <v>0.4878964158378682</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C272">
+        <v>0.4690831556503198</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>0.4675534058847239</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C274">
+        <v>0.4631261011829851</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C275">
+        <v>0.4548719176442423</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C276">
+        <v>0.4514308746473196</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C277">
+        <v>0.4403398020419297</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C278">
+        <v>0.4325461772270283</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C279">
+        <v>0.4316006755488835</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C280">
+        <v>0.4316006755488835</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C281">
+        <v>0.4311774461028192</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C282">
+        <v>0.4231130865885973</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C283">
+        <v>0.4189702833448514</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C284">
+        <v>0.4128354287858885</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C285">
+        <v>0.411477478466012</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C286">
+        <v>0.4111245465538089</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C287">
+        <v>0.4069906631553747</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C288">
+        <v>0.4027183488547697</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C289">
+        <v>0.4013716779674226</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C290">
+        <v>0.3973738769868694</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C291">
+        <v>0.3950203495331578</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C292">
+        <v>0.3896812407450705</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C293">
+        <v>0.3887353144436766</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C294">
+        <v>0.3885335228618811</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C295">
+        <v>0.3876164107727159</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C296">
+        <v>0.3830500359109409</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C297">
+        <v>0.378559280188731</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C298">
+        <v>0.371458189357291</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C299">
+        <v>0.3674804933299773</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C300">
+        <v>0.3565396884969038</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C301">
+        <v>0.3565396884969038</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C302">
+        <v>0.3385731559854897</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C303">
+        <v>0.3376356953585777</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C304">
+        <v>0.3376356953585777</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C305">
+        <v>0.3346683491523564</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C306">
+        <v>0.3239460953697305</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C307">
+        <v>0.3109882515549413</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C308">
+        <v>0.3034447388665698</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C309">
+        <v>0.2982668278919791</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C310">
+        <v>0.2982668278919791</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C311">
+        <v>0.2948969997435678</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C312">
+        <v>0.291970802919708</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C313">
+        <v>0.2902055622732769</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C314">
+        <v>0.2844673057439015</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C315">
+        <v>0.2844673057439015</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C316">
+        <v>0.2718348854769695</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C317">
+        <v>0.2649799128130609</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C318">
+        <v>0.2586206896551724</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C319">
+        <v>0.2251829611559392</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C320">
+        <v>0.219454655181873</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C321">
+        <v>0.2063931537880695</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C322">
+        <v>0.174104124408384</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C323">
+        <v>0.1688872208669544</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C324">
+        <v>0.1539919450367211</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C325">
+        <v>0.1316734498443859</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C326">
+        <v>0.120918984280532</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C327">
+        <v>0.116620594333103</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C328">
+        <v>0.1079820317899102</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C329">
+        <v>0.09340120487554289</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C330">
+        <v>0.08572987296391552</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C331">
+        <v>0.07550969041026932</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C332">
+        <v>0.06870409855484483</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C333">
+        <v>0.06449012494961709</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C334">
+        <v>0.06234899851921129</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C335">
+        <v>0.05983417386101376</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C336">
+        <v>0.0562957402889848</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C337">
+        <v>0.04670060243777144</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C338">
+        <v>0.03753049352598987</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C339">
+        <v>0.03419095649200787</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C340">
+        <v>0.03291819827728096</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C341">
+        <v>0.03020387616410773</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C342">
+        <v>0.02394062724443381</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C343">
+        <v>0.01915708812260536</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C344">
+        <v>0.01876524676299493</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C345">
+        <v>0.0101419878296146</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C346">
+        <v>0.009340120487554289</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C347">
+        <v>0.007793624814901411</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C348">
+        <v>0.007107320540156361</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C349">
+        <v>0.007005090365665717</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C350">
+        <v>0.004319281271596406</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C351">
+        <v>0.002369106846718787</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C375">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
